--- a/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
+++ b/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vandalsuidaho-my.sharepoint.com/personal/huck4481_vandals_uidaho_edu/Documents/Desktop/Research/Presentations and Summaries/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\experiments\armor_removal_experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{9D1D813D-7B1B-4A41-A0EC-A80AAF052777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10B31506-65E1-47F0-A309-AEA834E706E6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60C4CEC-8B61-4F74-962E-1CC6043AEF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15870" xr2:uid="{FA091B27-2BB3-44B8-A3BE-335E370FA65E}"/>
+    <workbookView xWindow="8880" yWindow="1605" windowWidth="17280" windowHeight="8880" xr2:uid="{FA091B27-2BB3-44B8-A3BE-335E370FA65E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
   <si>
     <t>Exp 1</t>
   </si>
@@ -131,6 +131,9 @@
   <si>
     <t>DOC (mg/L)</t>
   </si>
+  <si>
+    <t>PP (mg/L)</t>
+  </si>
 </sst>
 </file>
 
@@ -156,12 +159,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -191,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -202,16 +211,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -220,6 +220,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,55 +438,55 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.4553255204584259</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>19.697185438321707</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.18</c:v>
+                  <c:v>52.651576833306279</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.18</c:v>
+                  <c:v>89.933968747198861</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80.87</c:v>
+                  <c:v>73.619940199502565</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>220.02</c:v>
+                  <c:v>240.0916933100078</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>41.39</c:v>
+                  <c:v>73.574494175352541</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>20.816385127051692</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>17.667101333445487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>15.963635379745167</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>7.0668603509873824</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>12.436951564983044</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>8.095527221210272</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>10.855405992184116</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>6.0885448377837434</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>11.464181780769531</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -666,6 +670,188 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-964C-4193-8312-463578F34228}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>DOC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$3:$J$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>2.1269999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.643</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5389999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.502</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.46</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4370000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6559999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7370000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.4590000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.7050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.7070000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.681</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.262</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DFC1-4385-BA1E-DCFA7A011513}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -796,7 +982,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$3:$G$18</c:f>
+              <c:f>Sheet1!$H$3:$H$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -978,7 +1164,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$18</c:f>
+              <c:f>Sheet1!$I$3:$I$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -1162,8 +1348,9 @@
       <c:valAx>
         <c:axId val="506695151"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:min val="0"/>
+          <c:min val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1199,7 +1386,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="es-AR"/>
-                  <a:t>POC</a:t>
+                  <a:t>POC, DOC</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="es-AR" baseline="0"/>
@@ -1235,7 +1422,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1423,6 +1610,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1430,7 +1618,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1624,55 +1811,55 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.4553255204584259</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>19.697185438321707</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.18</c:v>
+                  <c:v>52.651576833306279</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.18</c:v>
+                  <c:v>89.933968747198861</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80.87</c:v>
+                  <c:v>73.619940199502565</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>220.02</c:v>
+                  <c:v>240.0916933100078</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>41.39</c:v>
+                  <c:v>73.574494175352541</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>20.816385127051692</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>17.667101333445487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>15.963635379745167</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>7.0668603509873824</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>12.436951564983044</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>8.095527221210272</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>10.855405992184116</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>6.0885448377837434</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>11.464181780769531</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1833,7 +2020,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2001,6 +2188,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2008,7 +2196,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2202,62 +2389,62 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.4553255204584259</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>19.697185438321707</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.18</c:v>
+                  <c:v>52.651576833306279</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.18</c:v>
+                  <c:v>89.933968747198861</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80.87</c:v>
+                  <c:v>73.619940199502565</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>220.02</c:v>
+                  <c:v>240.0916933100078</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>41.39</c:v>
+                  <c:v>73.574494175352541</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>20.816385127051692</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>17.667101333445487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>15.963635379745167</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>7.0668603509873824</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>12.436951564983044</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>8.095527221210272</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>10.855405992184116</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>6.0885448377837434</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>11.464181780769531</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$3:$G$18</c:f>
+              <c:f>Sheet1!$H$3:$H$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -2411,7 +2598,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2579,6 +2766,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2586,7 +2774,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2780,62 +2967,62 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.4553255204584259</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>19.697185438321707</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.18</c:v>
+                  <c:v>52.651576833306279</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.18</c:v>
+                  <c:v>89.933968747198861</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80.87</c:v>
+                  <c:v>73.619940199502565</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>220.02</c:v>
+                  <c:v>240.0916933100078</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>41.39</c:v>
+                  <c:v>73.574494175352541</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>20.816385127051692</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>17.667101333445487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>15.963635379745167</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>7.0668603509873824</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>12.436951564983044</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>8.095527221210272</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>10.855405992184116</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>6.0885448377837434</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>11.464181780769531</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$18</c:f>
+              <c:f>Sheet1!$I$3:$I$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -2989,7 +3176,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3157,6 +3344,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3164,7 +3352,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3358,62 +3545,62 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>3.4553255204584259</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>19.697185438321707</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.18</c:v>
+                  <c:v>52.651576833306279</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.18</c:v>
+                  <c:v>89.933968747198861</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>80.87</c:v>
+                  <c:v>73.619940199502565</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>220.02</c:v>
+                  <c:v>240.0916933100078</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>41.39</c:v>
+                  <c:v>73.574494175352541</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>20.816385127051692</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>17.667101333445487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>15.963635379745167</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>7.0668603509873824</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>12.436951564983044</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>8.095527221210272</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>10.855405992184116</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>6.0885448377837434</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>11.464181780769531</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$18</c:f>
+              <c:f>Sheet1!$J$3:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
@@ -3567,7 +3754,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3735,6 +3922,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3742,7 +3930,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6521,13 +6708,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>386724</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>71999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>372718</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>182704</xdr:rowOff>
@@ -6558,15 +6745,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>448235</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>11206</xdr:rowOff>
+      <xdr:colOff>378423</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>161700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>369794</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>5137</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>299982</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>155632</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7325,13 +7512,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>412668</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>44825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>145675</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
@@ -7363,13 +7550,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>437031</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>78442</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>15457</xdr:rowOff>
@@ -7402,15 +7589,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>470646</xdr:colOff>
+      <xdr:colOff>397023</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
+      <xdr:rowOff>60849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>369793</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>299980</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>60280</xdr:rowOff>
+      <xdr:rowOff>82020</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7441,9 +7628,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7481,7 +7668,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -7587,7 +7774,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7729,7 +7916,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7737,19 +7924,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52219DAC-46AB-4F48-9B56-23A99797F3FA}">
-  <dimension ref="A2:I20"/>
+  <dimension ref="A2:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" customWidth="1"/>
     <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="6" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -7759,26 +7946,29 @@
       <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -7788,26 +7978,29 @@
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="7">
+        <v>3.4553255204584259</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1.1019061775871011</v>
+      </c>
+      <c r="F3" s="1">
         <v>0</v>
       </c>
-      <c r="E3" s="5">
-        <v>1.1019061775871011</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="G3" s="1">
+        <v>5.1576641217063925E-5</v>
+      </c>
+      <c r="H3" s="1">
         <v>2.3E-2</v>
       </c>
-      <c r="H3" s="7">
+      <c r="I3" s="1">
         <v>0.03</v>
       </c>
-      <c r="I3" s="8">
+      <c r="J3" s="5">
         <v>2.1269999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -7818,26 +8011,29 @@
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="7">
+        <v>19.697185438321707</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.74367490551410131</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="1">
+        <v>2.9040962645844913E-4</v>
+      </c>
+      <c r="H4" s="1">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H4" s="7">
+      <c r="I4" s="1">
         <v>3.9E-2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="J4" s="5">
         <v>1.3859999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -7848,27 +8044,30 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="1">
-        <v>37.18</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="7">
+        <v>52.651576833306279</v>
+      </c>
+      <c r="E5" s="4">
         <v>8.5089648231025539</v>
       </c>
       <c r="F5" s="1">
         <f>F4+3</f>
         <v>6</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="1">
+        <v>6.6106276627512963E-4</v>
+      </c>
+      <c r="H5" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="H5" s="7">
+      <c r="I5" s="1">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="I5" s="8">
+      <c r="J5" s="5">
         <v>1.5820000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -7879,27 +8078,30 @@
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="1">
-        <v>52.18</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6" s="7">
+        <v>89.933968747198861</v>
+      </c>
+      <c r="E6" s="4">
         <v>10.416461895026821</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" ref="F6:F18" si="1">F5+3</f>
         <v>9</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="1">
+        <v>2.2224172067829232E-3</v>
+      </c>
+      <c r="H6" s="1">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H6" s="7">
+      <c r="I6" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="I6" s="8">
+      <c r="J6" s="5">
         <v>1.643</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -7910,27 +8112,30 @@
       <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1">
-        <v>80.87</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7" s="7">
+        <v>73.619940199502565</v>
+      </c>
+      <c r="E7" s="4">
         <v>9.7361003162332747</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="1">
+        <v>2.0552078586848492E-3</v>
+      </c>
+      <c r="H7" s="1">
         <v>1.9E-2</v>
       </c>
-      <c r="H7" s="7">
+      <c r="I7" s="1">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="I7" s="8">
+      <c r="J7" s="5">
         <v>1.5389999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -7941,27 +8146,30 @@
       <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1">
-        <v>220.02</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="7">
+        <v>240.0916933100078</v>
+      </c>
+      <c r="E8" s="4">
         <v>38.658748032082826</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="1">
+        <v>2.3927254516111322E-3</v>
+      </c>
+      <c r="H8" s="1">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="H8" s="7">
+      <c r="I8" s="1">
         <v>0.11799999999999999</v>
       </c>
-      <c r="I8" s="8">
+      <c r="J8" s="5">
         <v>1.502</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -7972,27 +8180,30 @@
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="1">
-        <v>41.39</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9" s="7">
+        <v>73.574494175352541</v>
+      </c>
+      <c r="E9" s="4">
         <v>6.3447902158703471</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="1">
+        <v>2.5382950090458741E-4</v>
+      </c>
+      <c r="H9" s="1">
         <v>1.9E-2</v>
       </c>
-      <c r="H9" s="7">
+      <c r="I9" s="1">
         <v>0.05</v>
       </c>
-      <c r="I9" s="8">
+      <c r="J9" s="5">
         <v>1.46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -8003,27 +8214,30 @@
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="7">
+        <v>20.816385127051692</v>
+      </c>
+      <c r="E10" s="4">
         <v>1.9795058998944075</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="1">
+        <v>3.8420401139033575E-4</v>
+      </c>
+      <c r="H10" s="1">
         <v>1.9E-2</v>
       </c>
-      <c r="H10" s="7">
+      <c r="I10" s="1">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I10" s="8">
+      <c r="J10" s="5">
         <v>1.4370000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -8034,27 +8248,30 @@
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="7">
+        <v>17.667101333445487</v>
+      </c>
+      <c r="E11" s="4">
         <v>3.219264329662352</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="1">
+        <v>4.6887855651876298E-5</v>
+      </c>
+      <c r="H11" s="1">
         <v>1.9E-2</v>
       </c>
-      <c r="H11" s="7">
+      <c r="I11" s="1">
         <v>0.03</v>
       </c>
-      <c r="I11" s="8">
+      <c r="J11" s="5">
         <v>1.6559999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -8065,27 +8282,30 @@
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="1">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="7">
+        <v>15.963635379745167</v>
+      </c>
+      <c r="E12" s="4">
         <v>3.005177966008191</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="1">
+        <v>1.2779120936401461E-4</v>
+      </c>
+      <c r="H12" s="1">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H12" s="7">
+      <c r="I12" s="1">
         <v>2.7E-2</v>
       </c>
-      <c r="I12" s="8">
+      <c r="J12" s="5">
         <v>1.7370000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -8096,27 +8316,30 @@
       <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" s="7">
+        <v>7.0668603509873824</v>
+      </c>
+      <c r="E13" s="4">
         <v>1.5626443518739146</v>
       </c>
       <c r="F13" s="1">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="1">
+        <v>4.4474966741118462E-6</v>
+      </c>
+      <c r="H13" s="1">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H13" s="7">
+      <c r="I13" s="1">
         <v>2.7E-2</v>
       </c>
-      <c r="I13" s="8">
+      <c r="J13" s="5">
         <v>1.4590000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -8127,27 +8350,30 @@
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14" s="7">
+        <v>12.436951564983044</v>
+      </c>
+      <c r="E14" s="4">
         <v>2.8765823670330759</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="1">
+        <v>4.6887855651876298E-5</v>
+      </c>
+      <c r="H14" s="1">
         <v>1.9E-2</v>
       </c>
-      <c r="H14" s="7">
+      <c r="I14" s="1">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="I14" s="8">
+      <c r="J14" s="5">
         <v>1.6379999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -8158,27 +8384,30 @@
       <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15" s="7">
+        <v>8.095527221210272</v>
+      </c>
+      <c r="E15" s="4">
         <v>2.2126150321267621</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="1">
+        <v>1.4986210786444661E-4</v>
+      </c>
+      <c r="H15" s="1">
         <v>0.02</v>
       </c>
-      <c r="H15" s="7">
+      <c r="I15" s="1">
         <v>3.1E-2</v>
       </c>
-      <c r="I15" s="8">
+      <c r="J15" s="5">
         <v>1.7050000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -8189,27 +8418,30 @@
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="D16" s="7">
+        <v>10.855405992184116</v>
+      </c>
+      <c r="E16" s="4">
         <v>2.5675322748057079</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="1">
+        <v>5.1576641217063925E-5</v>
+      </c>
+      <c r="H16" s="1">
         <v>0.02</v>
       </c>
-      <c r="H16" s="7">
+      <c r="I16" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="I16" s="8">
+      <c r="J16" s="5">
         <v>1.7070000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -8220,27 +8452,30 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="D17" s="7">
+        <v>6.0885448377837434</v>
+      </c>
+      <c r="E17" s="4">
         <v>2.2312408401110857</v>
       </c>
       <c r="F17" s="1">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="1">
+        <v>4.8981773007164672E-4</v>
+      </c>
+      <c r="H17" s="1">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="H17" s="7">
+      <c r="I17" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I17" s="8">
+      <c r="J17" s="5">
         <v>1.681</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -8251,32 +8486,45 @@
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" s="7">
+        <v>11.464181780769531</v>
+      </c>
+      <c r="E18" s="4">
         <v>2.7825557685143458</v>
       </c>
       <c r="F18" s="1">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="1">
+        <v>4.9120610682918029E-5</v>
+      </c>
+      <c r="H18" s="1">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="H18" s="7">
+      <c r="I18" s="1">
         <v>0.03</v>
       </c>
-      <c r="I18" s="8">
+      <c r="J18" s="5">
         <v>1.262</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D19" s="8">
+        <f>AVERAGE(D12:D18)</f>
+        <v>10.281586732523323</v>
+      </c>
+      <c r="E19" s="8">
+        <f>AVERAGE(E13:E18)</f>
+        <v>2.3721951057441486</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
+++ b/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\experiments\armor_removal_experiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\experiments\armor_removal_experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60C4CEC-8B61-4F74-962E-1CC6043AEF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F926A568-F551-4281-8F45-F9C54FBEB5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8880" yWindow="1605" windowWidth="17280" windowHeight="8880" xr2:uid="{FA091B27-2BB3-44B8-A3BE-335E370FA65E}"/>
+    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" xr2:uid="{FA091B27-2BB3-44B8-A3BE-335E370FA65E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -217,13 +217,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7924,7 +7924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52219DAC-46AB-4F48-9B56-23A99797F3FA}">
-  <dimension ref="A2:J20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
@@ -7936,6 +7936,36 @@
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D1" s="7">
+        <f>MAX(D3:D18)</f>
+        <v>240.0916933100078</v>
+      </c>
+      <c r="E1" s="7">
+        <f t="shared" ref="E1:J1" si="0">MAX(E3:E18)</f>
+        <v>38.658748032082826</v>
+      </c>
+      <c r="F1" s="7">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G1" s="7">
+        <f t="shared" si="0"/>
+        <v>2.3927254516111322E-3</v>
+      </c>
+      <c r="H1" s="7">
+        <f t="shared" si="0"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="I1" s="7">
+        <f t="shared" si="0"/>
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="J1" s="7">
+        <f t="shared" si="0"/>
+        <v>2.1269999999999998</v>
+      </c>
+    </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>17</v>
@@ -7978,7 +8008,7 @@
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>3.4553255204584259</v>
       </c>
       <c r="E3" s="4">
@@ -8011,7 +8041,7 @@
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>19.697185438321707</v>
       </c>
       <c r="E4" s="4">
@@ -8038,13 +8068,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" ref="B5:B18" si="0">B4+0.00211111111111</f>
+        <f t="shared" ref="B5:B18" si="1">B4+0.00211111111111</f>
         <v>0.73061111111110877</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>52.651576833306279</v>
       </c>
       <c r="E5" s="4">
@@ -8072,20 +8102,20 @@
         <v>3</v>
       </c>
       <c r="B6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.73272222222221872</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>89.933968747198861</v>
       </c>
       <c r="E6" s="4">
         <v>10.416461895026821</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" ref="F6:F18" si="1">F5+3</f>
+        <f t="shared" ref="F6:F18" si="2">F5+3</f>
         <v>9</v>
       </c>
       <c r="G6" s="1">
@@ -8106,20 +8136,20 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.73483333333332868</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>73.619940199502565</v>
       </c>
       <c r="E7" s="4">
         <v>9.7361003162332747</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="G7" s="1">
@@ -8140,20 +8170,20 @@
         <v>5</v>
       </c>
       <c r="B8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.73694444444443863</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>240.0916933100078</v>
       </c>
       <c r="E8" s="4">
         <v>38.658748032082826</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="G8" s="1">
@@ -8174,20 +8204,20 @@
         <v>6</v>
       </c>
       <c r="B9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.73905555555554858</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>73.574494175352541</v>
       </c>
       <c r="E9" s="4">
         <v>6.3447902158703471</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="G9" s="1">
@@ -8208,20 +8238,20 @@
         <v>7</v>
       </c>
       <c r="B10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.74116666666665854</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>20.816385127051692</v>
       </c>
       <c r="E10" s="4">
         <v>1.9795058998944075</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="G10" s="1">
@@ -8242,20 +8272,20 @@
         <v>8</v>
       </c>
       <c r="B11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.74327777777776849</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>17.667101333445487</v>
       </c>
       <c r="E11" s="4">
         <v>3.219264329662352</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="G11" s="1">
@@ -8276,20 +8306,20 @@
         <v>9</v>
       </c>
       <c r="B12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.74538888888887844</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>15.963635379745167</v>
       </c>
       <c r="E12" s="4">
         <v>3.005177966008191</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="G12" s="1">
@@ -8310,20 +8340,20 @@
         <v>10</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.7474999999999884</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>7.0668603509873824</v>
       </c>
       <c r="E13" s="4">
         <v>1.5626443518739146</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="G13" s="1">
@@ -8344,20 +8374,20 @@
         <v>11</v>
       </c>
       <c r="B14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.74961111111109835</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>12.436951564983044</v>
       </c>
       <c r="E14" s="4">
         <v>2.8765823670330759</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="G14" s="1">
@@ -8378,20 +8408,20 @@
         <v>12</v>
       </c>
       <c r="B15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.7517222222222083</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>8.095527221210272</v>
       </c>
       <c r="E15" s="4">
         <v>2.2126150321267621</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="G15" s="1">
@@ -8412,20 +8442,20 @@
         <v>13</v>
       </c>
       <c r="B16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.75383333333331826</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>10.855405992184116</v>
       </c>
       <c r="E16" s="4">
         <v>2.5675322748057079</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="G16" s="1">
@@ -8446,20 +8476,20 @@
         <v>14</v>
       </c>
       <c r="B17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.75594444444442821</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>6.0885448377837434</v>
       </c>
       <c r="E17" s="4">
         <v>2.2312408401110857</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="G17" s="1">
@@ -8480,20 +8510,20 @@
         <v>15</v>
       </c>
       <c r="B18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.75805555555553816</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>11.464181780769531</v>
       </c>
       <c r="E18" s="4">
         <v>2.7825557685143458</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="G18" s="1">
@@ -8510,21 +8540,21 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f>AVERAGE(D12:D18)</f>
         <v>10.281586732523323</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <f>AVERAGE(E13:E18)</f>
         <v>2.3721951057441486</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
+++ b/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\experiments\armor_removal_experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F926A568-F551-4281-8F45-F9C54FBEB5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C394D13-FE17-4A32-8391-6BF29FE5C4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" xr2:uid="{FA091B27-2BB3-44B8-A3BE-335E370FA65E}"/>
   </bookViews>
@@ -211,17 +211,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -262,32 +262,42 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx2"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="es-AR"/>
+              <a:rPr lang="es-AR" b="0" i="0">
+                <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t>Experimental</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="es-AR" baseline="0"/>
+              <a:rPr lang="es-AR" b="0" i="0" baseline="0">
+                <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t> c</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="es-AR"/>
+              <a:rPr lang="es-AR" b="0" i="0">
+                <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t>onstituent</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="es-AR" baseline="0"/>
+              <a:rPr lang="es-AR" b="0" i="0" baseline="0">
+                <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
               <a:t> concentrations </a:t>
             </a:r>
-            <a:endParaRPr lang="es-AR"/>
+            <a:endParaRPr lang="es-AR" b="0" i="0">
+              <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -304,11 +314,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx2"/>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -438,7 +448,7 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>3.4553255204584259</c:v>
@@ -613,7 +623,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$18</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>1.1019061775871011</c:v>
@@ -1048,7 +1058,7 @@
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
-            <c:v>TP</c:v>
+            <c:v>PP</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="9525" cap="rnd">
@@ -1164,57 +1174,57 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$18</c:f>
+              <c:f>Sheet1!$G$3:$G$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.03</c:v>
+                  <c:v>5.1576641217063925E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.9E-2</c:v>
+                  <c:v>2.9040962645844913E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.5999999999999999E-2</c:v>
+                  <c:v>6.6106276627512963E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.1999999999999995E-2</c:v>
+                  <c:v>2.2224172067829232E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.1000000000000003E-2</c:v>
+                  <c:v>2.0552078586848492E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.11799999999999999</c:v>
+                  <c:v>2.3927254516111322E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.05</c:v>
+                  <c:v>2.5382950090458741E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.3000000000000002E-2</c:v>
+                  <c:v>3.8420401139033575E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.03</c:v>
+                  <c:v>4.6887855651876298E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.7E-2</c:v>
+                  <c:v>1.2779120936401461E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.7E-2</c:v>
+                  <c:v>4.4474966741118462E-6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.5999999999999999E-2</c:v>
+                  <c:v>4.6887855651876298E-5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.1E-2</c:v>
+                  <c:v>1.4986210786444661E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.4E-2</c:v>
+                  <c:v>5.1576641217063925E-5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.5000000000000001E-2</c:v>
+                  <c:v>4.8981773007164672E-4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.03</c:v>
+                  <c:v>4.9120610682918029E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1269,13 +1279,15 @@
                     <a:solidFill>
                       <a:schemeClr val="tx2"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="es-AR"/>
+                  <a:rPr lang="es-AR">
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
                   <a:t>Time elapsed</a:t>
                 </a:r>
               </a:p>
@@ -1298,7 +1310,7 @@
                   <a:solidFill>
                     <a:schemeClr val="tx2"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
@@ -1379,20 +1391,26 @@
                     <a:solidFill>
                       <a:schemeClr val="tx2"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="es-AR"/>
+                  <a:rPr lang="es-AR">
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
                   <a:t>POC, DOC</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="es-AR" baseline="0"/>
+                  <a:rPr lang="es-AR" baseline="0">
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
                   <a:t> and SS (mg/L)</a:t>
                 </a:r>
-                <a:endParaRPr lang="es-AR"/>
+                <a:endParaRPr lang="es-AR">
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1413,7 +1431,7 @@
                   <a:solidFill>
                     <a:schemeClr val="tx2"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
@@ -1462,6 +1480,7 @@
       <c:valAx>
         <c:axId val="1879921696"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -1477,20 +1496,26 @@
                     <a:solidFill>
                       <a:schemeClr val="tx2"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="es-AR"/>
-                  <a:t>SRP and TP</a:t>
+                  <a:rPr lang="es-AR">
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>SRP and PP</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="es-AR" baseline="0"/>
+                  <a:rPr lang="es-AR" baseline="0">
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
                   <a:t> (mg/L)</a:t>
                 </a:r>
-                <a:endParaRPr lang="es-AR"/>
+                <a:endParaRPr lang="es-AR">
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1511,7 +1536,7 @@
                   <a:solidFill>
                     <a:schemeClr val="tx2"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
@@ -1811,7 +1836,7 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>3.4553255204584259</c:v>
@@ -1868,7 +1893,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$18</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>1.1019061775871011</c:v>
@@ -2020,7 +2045,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2137,7 +2162,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2389,7 +2414,7 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>3.4553255204584259</c:v>
@@ -2598,7 +2623,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2967,7 +2992,7 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>3.4553255204584259</c:v>
@@ -3176,7 +3201,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3545,7 +3570,7 @@
             <c:numRef>
               <c:f>Sheet1!$D$3:$D$18</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>3.4553255204584259</c:v>
@@ -3754,7 +3779,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -7927,6 +7952,7 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" customWidth="1"/>
     <col min="5" max="5" width="17.28515625" customWidth="1"/>
@@ -7937,31 +7963,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D1" s="7">
+      <c r="D1" s="5">
         <f>MAX(D3:D18)</f>
         <v>240.0916933100078</v>
       </c>
-      <c r="E1" s="7">
+      <c r="E1" s="5">
         <f t="shared" ref="E1:J1" si="0">MAX(E3:E18)</f>
         <v>38.658748032082826</v>
       </c>
-      <c r="F1" s="7">
+      <c r="F1" s="5">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="G1" s="7">
+      <c r="G1" s="5">
         <f t="shared" si="0"/>
         <v>2.3927254516111322E-3</v>
       </c>
-      <c r="H1" s="7">
+      <c r="H1" s="5">
         <f t="shared" si="0"/>
         <v>2.4E-2</v>
       </c>
-      <c r="I1" s="7">
+      <c r="I1" s="5">
         <f t="shared" si="0"/>
         <v>0.11799999999999999</v>
       </c>
-      <c r="J1" s="7">
+      <c r="J1" s="5">
         <f t="shared" si="0"/>
         <v>2.1269999999999998</v>
       </c>
@@ -8008,7 +8034,7 @@
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
         <v>3.4553255204584259</v>
       </c>
       <c r="E3" s="4">
@@ -8017,7 +8043,7 @@
       <c r="F3" s="1">
         <v>0</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="8">
         <v>5.1576641217063925E-5</v>
       </c>
       <c r="H3" s="1">
@@ -8026,7 +8052,7 @@
       <c r="I3" s="1">
         <v>0.03</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2.1269999999999998</v>
       </c>
     </row>
@@ -8041,7 +8067,7 @@
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <v>19.697185438321707</v>
       </c>
       <c r="E4" s="4">
@@ -8050,7 +8076,7 @@
       <c r="F4" s="1">
         <v>3</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="8">
         <v>2.9040962645844913E-4</v>
       </c>
       <c r="H4" s="1">
@@ -8059,7 +8085,7 @@
       <c r="I4" s="1">
         <v>3.9E-2</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>1.3859999999999999</v>
       </c>
     </row>
@@ -8074,7 +8100,7 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>52.651576833306279</v>
       </c>
       <c r="E5" s="4">
@@ -8084,7 +8110,7 @@
         <f>F4+3</f>
         <v>6</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="8">
         <v>6.6106276627512963E-4</v>
       </c>
       <c r="H5" s="1">
@@ -8093,7 +8119,7 @@
       <c r="I5" s="1">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>1.5820000000000001</v>
       </c>
     </row>
@@ -8108,7 +8134,7 @@
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>89.933968747198861</v>
       </c>
       <c r="E6" s="4">
@@ -8118,7 +8144,7 @@
         <f t="shared" ref="F6:F18" si="2">F5+3</f>
         <v>9</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="8">
         <v>2.2224172067829232E-3</v>
       </c>
       <c r="H6" s="1">
@@ -8127,7 +8153,7 @@
       <c r="I6" s="1">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>1.643</v>
       </c>
     </row>
@@ -8142,7 +8168,7 @@
       <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>73.619940199502565</v>
       </c>
       <c r="E7" s="4">
@@ -8152,7 +8178,7 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="8">
         <v>2.0552078586848492E-3</v>
       </c>
       <c r="H7" s="1">
@@ -8161,7 +8187,7 @@
       <c r="I7" s="1">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>1.5389999999999999</v>
       </c>
     </row>
@@ -8176,7 +8202,7 @@
       <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>240.0916933100078</v>
       </c>
       <c r="E8" s="4">
@@ -8186,7 +8212,7 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="8">
         <v>2.3927254516111322E-3</v>
       </c>
       <c r="H8" s="1">
@@ -8195,7 +8221,7 @@
       <c r="I8" s="1">
         <v>0.11799999999999999</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>1.502</v>
       </c>
     </row>
@@ -8210,7 +8236,7 @@
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>73.574494175352541</v>
       </c>
       <c r="E9" s="4">
@@ -8220,7 +8246,7 @@
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="8">
         <v>2.5382950090458741E-4</v>
       </c>
       <c r="H9" s="1">
@@ -8229,7 +8255,7 @@
       <c r="I9" s="1">
         <v>0.05</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>1.46</v>
       </c>
     </row>
@@ -8244,7 +8270,7 @@
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>20.816385127051692</v>
       </c>
       <c r="E10" s="4">
@@ -8254,7 +8280,7 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="8">
         <v>3.8420401139033575E-4</v>
       </c>
       <c r="H10" s="1">
@@ -8263,7 +8289,7 @@
       <c r="I10" s="1">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>1.4370000000000001</v>
       </c>
     </row>
@@ -8278,7 +8304,7 @@
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>17.667101333445487</v>
       </c>
       <c r="E11" s="4">
@@ -8288,7 +8314,7 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="8">
         <v>4.6887855651876298E-5</v>
       </c>
       <c r="H11" s="1">
@@ -8297,7 +8323,7 @@
       <c r="I11" s="1">
         <v>0.03</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>1.6559999999999999</v>
       </c>
     </row>
@@ -8312,7 +8338,7 @@
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>15.963635379745167</v>
       </c>
       <c r="E12" s="4">
@@ -8322,7 +8348,7 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="8">
         <v>1.2779120936401461E-4</v>
       </c>
       <c r="H12" s="1">
@@ -8331,7 +8357,7 @@
       <c r="I12" s="1">
         <v>2.7E-2</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1.7370000000000001</v>
       </c>
     </row>
@@ -8346,7 +8372,7 @@
       <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>7.0668603509873824</v>
       </c>
       <c r="E13" s="4">
@@ -8356,7 +8382,7 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="8">
         <v>4.4474966741118462E-6</v>
       </c>
       <c r="H13" s="1">
@@ -8365,7 +8391,7 @@
       <c r="I13" s="1">
         <v>2.7E-2</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>1.4590000000000001</v>
       </c>
     </row>
@@ -8380,7 +8406,7 @@
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>12.436951564983044</v>
       </c>
       <c r="E14" s="4">
@@ -8390,7 +8416,7 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="8">
         <v>4.6887855651876298E-5</v>
       </c>
       <c r="H14" s="1">
@@ -8399,7 +8425,7 @@
       <c r="I14" s="1">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="4">
         <v>1.6379999999999999</v>
       </c>
     </row>
@@ -8414,7 +8440,7 @@
       <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>8.095527221210272</v>
       </c>
       <c r="E15" s="4">
@@ -8424,7 +8450,7 @@
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="8">
         <v>1.4986210786444661E-4</v>
       </c>
       <c r="H15" s="1">
@@ -8433,7 +8459,7 @@
       <c r="I15" s="1">
         <v>3.1E-2</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="4">
         <v>1.7050000000000001</v>
       </c>
     </row>
@@ -8448,7 +8474,7 @@
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>10.855405992184116</v>
       </c>
       <c r="E16" s="4">
@@ -8458,7 +8484,7 @@
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="8">
         <v>5.1576641217063925E-5</v>
       </c>
       <c r="H16" s="1">
@@ -8467,7 +8493,7 @@
       <c r="I16" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="4">
         <v>1.7070000000000001</v>
       </c>
     </row>
@@ -8482,7 +8508,7 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="7">
         <v>6.0885448377837434</v>
       </c>
       <c r="E17" s="4">
@@ -8492,7 +8518,7 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="8">
         <v>4.8981773007164672E-4</v>
       </c>
       <c r="H17" s="1">
@@ -8501,7 +8527,7 @@
       <c r="I17" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="4">
         <v>1.681</v>
       </c>
     </row>
@@ -8516,7 +8542,7 @@
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="7">
         <v>11.464181780769531</v>
       </c>
       <c r="E18" s="4">
@@ -8526,7 +8552,7 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="8">
         <v>4.9120610682918029E-5</v>
       </c>
       <c r="H18" s="1">
@@ -8535,26 +8561,26 @@
       <c r="I18" s="1">
         <v>0.03</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="4">
         <v>1.262</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <f>AVERAGE(D12:D18)</f>
         <v>10.281586732523323</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <f>AVERAGE(E13:E18)</f>
         <v>2.3721951057441486</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
+++ b/experiments/armor_removal_experiment/Experiment_Summer2021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\experiments\armor_removal_experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C394D13-FE17-4A32-8391-6BF29FE5C4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8F79ED-55D8-475D-AD7E-00F08B19AA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" xr2:uid="{FA091B27-2BB3-44B8-A3BE-335E370FA65E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>Exp 1</t>
   </si>
@@ -134,6 +134,12 @@
   <si>
     <t>PP (mg/L)</t>
   </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
 </sst>
 </file>
 
@@ -200,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,13 +221,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3989,6 +4010,2587 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>SS </c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$3:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>3.4553255204584259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.697185438321707</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.651576833306279</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89.933968747198861</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>73.619940199502565</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>240.0916933100078</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>73.574494175352541</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.816385127051692</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17.667101333445487</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15.963635379745167</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.0668603509873824</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.436951564983044</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.095527221210272</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10.855405992184116</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.0885448377837434</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>11.464181780769531</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0CA6-4688-B410-22A398F6614F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>POC </c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$3:$E$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>1.1019061775871011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.74367490551410131</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.5089648231025539</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.416461895026821</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.7361003162332747</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>38.658748032082826</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.3447902158703471</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9795058998944075</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.219264329662352</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.005177966008191</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.5626443518739146</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.8765823670330759</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2126150321267621</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.5675322748057079</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.2312408401110857</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.7825557685143458</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0CA6-4688-B410-22A398F6614F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>DOC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$3:$J$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>2.1269999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3859999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.643</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5389999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.502</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.46</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4370000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6559999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.7370000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.4590000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.6379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.7050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.7070000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.681</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.262</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0CA6-4688-B410-22A398F6614F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="506693071"/>
+        <c:axId val="506695151"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>SRP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$3:$H$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0CA6-4688-B410-22A398F6614F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>PP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="15875" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$3:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>5.1576641217063925E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.9040962645844913E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6106276627512963E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2224172067829232E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0552078586848492E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3927254516111322E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5382950090458741E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.8420401139033575E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.6887855651876298E-5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2779120936401461E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.4474966741118462E-6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.6887855651876298E-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.4986210786444661E-4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.1576641217063925E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.8981773007164672E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.9120610682918029E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0CA6-4688-B410-22A398F6614F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1879922112"/>
+        <c:axId val="1879921696"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="506693071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>Time </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-AR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-AR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="506695151"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="506695151"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>POC, DOC</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t> and SS (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-AR" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-AR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-AR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="506693071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1879921696"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>SRP and PP</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t> (mg/L)</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-AR" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-AR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-AR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1879922112"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1879922112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1879921696"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-AR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-AR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>SS</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AO$4:$AO$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.7005296090622561</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.237805098699029</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.027640005178764</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21.306224193237586</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.484536808026789</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.293071735131701</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.0244353256447845</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.1130063517435405</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.6200091091930569</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0452082760786618</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.5993574241691144</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3429130405450831</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.1416449558546669</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.7620756139282536</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.3178297422028566</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4B97-4A46-84E6-E5B3C20D10FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>POC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AP$4:$AP$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.67489857180269497</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.7220411285242623</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.4531295920640606</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.8356890216850399</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35.08352055592956</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.7580131093954394</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7964377913090843</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.9215412302268198</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.7272539415186681</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.4181283158750546</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.6105510846051083</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.0079885902553296</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.3300824761940815</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.0248918514976886</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.5252202275582545</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4B97-4A46-84E6-E5B3C20D10FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>PP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AQ$4:$AQ$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.6306424692573476</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.817096086055709</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43.089607123304596</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>39.847648280068533</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46.391649303823002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.9214042425974984</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.4491863433562129</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.90909090909090917</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.4776954518266576</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.90909090909090917</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.9056197598005924</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.4968908116799291</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.95238095238095244</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4B97-4A46-84E6-E5B3C20D10FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>DOC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="60000"/>
+                    <a:alpha val="96000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AS$4:$AS$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.65162200282087446</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74377056887635173</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.77244945933239317</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.72355430183356839</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.7061589092618713</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.68641278796426897</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.67559943582510584</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.77856135401974613</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.81664315937940779</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.68594264221908807</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.77009873060648804</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.80159849553361551</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.80253878702397752</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.79031499764927138</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.59332393041842979</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4B97-4A46-84E6-E5B3C20D10FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>SRP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AR$4:$AR$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9565217391304347</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0434782608695652</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9565217391304347</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.82608695652173914</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.78260869565217384</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.82608695652173914</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.82608695652173914</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.82608695652173914</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.91304347826086962</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.9565217391304347</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.82608695652173914</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.86956521739130443</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.86956521739130443</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.9565217391304347</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.91304347826086962</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4B97-4A46-84E6-E5B3C20D10FE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="506693071"/>
+        <c:axId val="506695151"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="506693071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>Time (s) </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-AR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-AR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="506695151"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="506695151"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>Constituent</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-AR" sz="1400" b="0" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t> increase relative to base</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-AR" sz="1400" b="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-AR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-AR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="506693071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Abadi" panose="020B0604020104020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-AR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-AR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
   <a:schemeClr val="accent6"/>
@@ -4186,6 +6788,80 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
   <cs:axisTitle>
@@ -6725,6 +9401,964 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -6771,13 +10405,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>378423</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>161700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>299982</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>155632</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6807,13 +10441,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>560406</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>189940</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>527797</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>151840</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6865,13 +10499,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>489921</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>189940</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>614754</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>151840</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6923,13 +10557,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>173690</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>81355</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>179406</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>189940</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6993,13 +10627,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>794049</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>79450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>239469</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>188035</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7063,13 +10697,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>871257</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>79450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>238237</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>188035</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7133,13 +10767,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>268941</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>85165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>566121</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>81355</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7206,13 +10840,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>27005</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>165175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>287991</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>69925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7276,13 +10910,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>535641</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>12775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>463027</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>31825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -7329,13 +10963,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>581136</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>112059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>688152</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>32049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7397,13 +11031,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>268940</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>168985</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>165847</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>184225</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7471,13 +11105,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>908349</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>37540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>351864</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>127075</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7539,13 +11173,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>412668</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>44825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>145675</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>44824</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7577,13 +11211,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>437031</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>78442</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>15457</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7615,13 +11249,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>397023</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>60849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>299980</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>82020</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7644,6 +11278,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>43144</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72EEADE6-9354-48A6-BA6C-EC7887E7E61B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>323021</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0284ADDB-2C77-4095-B2E7-3DEC1C40DE8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7949,7 +11659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52219DAC-46AB-4F48-9B56-23A99797F3FA}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:AS25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.5703125" customWidth="1"/>
@@ -7960,9 +11670,15 @@
     <col min="8" max="8" width="17.28515625" customWidth="1"/>
     <col min="9" max="9" width="17.85546875" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="40" max="40" width="17.7109375" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" customWidth="1"/>
+    <col min="42" max="42" width="15.28515625" customWidth="1"/>
+    <col min="43" max="43" width="14.140625" customWidth="1"/>
+    <col min="44" max="44" width="14" customWidth="1"/>
+    <col min="45" max="45" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D1" s="5">
         <f>MAX(D3:D18)</f>
         <v>240.0916933100078</v>
@@ -7992,7 +11708,7 @@
         <v>2.1269999999999998</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -8024,7 +11740,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -8034,7 +11750,7 @@
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>3.4553255204584259</v>
       </c>
       <c r="E3" s="4">
@@ -8043,7 +11759,7 @@
       <c r="F3" s="1">
         <v>0</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>5.1576641217063925E-5</v>
       </c>
       <c r="H3" s="1">
@@ -8055,8 +11771,26 @@
       <c r="J3" s="4">
         <v>2.1269999999999998</v>
       </c>
+      <c r="AN3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -8067,7 +11801,7 @@
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>19.697185438321707</v>
       </c>
       <c r="E4" s="4">
@@ -8076,7 +11810,7 @@
       <c r="F4" s="1">
         <v>3</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>2.9040962645844913E-4</v>
       </c>
       <c r="H4" s="1">
@@ -8088,8 +11822,26 @@
       <c r="J4" s="4">
         <v>1.3859999999999999</v>
       </c>
+      <c r="AN4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="12">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="13">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="13">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="13">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="13">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -8100,7 +11852,7 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>52.651576833306279</v>
       </c>
       <c r="E5" s="4">
@@ -8110,7 +11862,7 @@
         <f>F4+3</f>
         <v>6</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>6.6106276627512963E-4</v>
       </c>
       <c r="H5" s="1">
@@ -8122,8 +11874,31 @@
       <c r="J5" s="4">
         <v>1.5820000000000001</v>
       </c>
+      <c r="AN5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="6">
+        <f>D4/$D$3</f>
+        <v>5.7005296090622561</v>
+      </c>
+      <c r="AP5" s="6">
+        <f>E4/E$3</f>
+        <v>0.67489857180269497</v>
+      </c>
+      <c r="AQ5" s="6">
+        <f>G4/G$3</f>
+        <v>5.6306424692573476</v>
+      </c>
+      <c r="AR5" s="6">
+        <f t="shared" ref="AR5:AS19" si="2">H4/H$3</f>
+        <v>0.9565217391304347</v>
+      </c>
+      <c r="AS5" s="6">
+        <f>J4/J$3</f>
+        <v>0.65162200282087446</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -8134,17 +11909,17 @@
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>89.933968747198861</v>
       </c>
       <c r="E6" s="4">
         <v>10.416461895026821</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" ref="F6:F18" si="2">F5+3</f>
+        <f t="shared" ref="F6:F18" si="3">F5+3</f>
         <v>9</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>2.2224172067829232E-3</v>
       </c>
       <c r="H6" s="1">
@@ -8156,8 +11931,32 @@
       <c r="J6" s="4">
         <v>1.643</v>
       </c>
+      <c r="AN6" s="1">
+        <f>AN5+3</f>
+        <v>6</v>
+      </c>
+      <c r="AO6" s="6">
+        <f t="shared" ref="AO6:AO19" si="4">D5/$D$3</f>
+        <v>15.237805098699029</v>
+      </c>
+      <c r="AP6" s="6">
+        <f t="shared" ref="AP6:AP19" si="5">E5/E$3</f>
+        <v>7.7220411285242623</v>
+      </c>
+      <c r="AQ6" s="6">
+        <f t="shared" ref="AQ6:AQ19" si="6">G5/G$3</f>
+        <v>12.817096086055709</v>
+      </c>
+      <c r="AR6" s="6">
+        <f t="shared" si="2"/>
+        <v>1.0434782608695652</v>
+      </c>
+      <c r="AS6" s="6">
+        <f t="shared" ref="AS6:AS19" si="7">J5/J$3</f>
+        <v>0.74377056887635173</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -8168,17 +11967,17 @@
       <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>73.619940199502565</v>
       </c>
       <c r="E7" s="4">
         <v>9.7361003162332747</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>2.0552078586848492E-3</v>
       </c>
       <c r="H7" s="1">
@@ -8190,8 +11989,32 @@
       <c r="J7" s="4">
         <v>1.5389999999999999</v>
       </c>
+      <c r="AN7" s="1">
+        <f t="shared" ref="AN7:AN19" si="8">AN6+3</f>
+        <v>9</v>
+      </c>
+      <c r="AO7" s="6">
+        <f t="shared" si="4"/>
+        <v>26.027640005178764</v>
+      </c>
+      <c r="AP7" s="6">
+        <f t="shared" si="5"/>
+        <v>9.4531295920640606</v>
+      </c>
+      <c r="AQ7" s="6">
+        <f t="shared" si="6"/>
+        <v>43.089607123304596</v>
+      </c>
+      <c r="AR7" s="6">
+        <f t="shared" si="2"/>
+        <v>0.9565217391304347</v>
+      </c>
+      <c r="AS7" s="6">
+        <f t="shared" si="7"/>
+        <v>0.77244945933239317</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -8202,17 +12025,17 @@
       <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>240.0916933100078</v>
       </c>
       <c r="E8" s="4">
         <v>38.658748032082826</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>2.3927254516111322E-3</v>
       </c>
       <c r="H8" s="1">
@@ -8224,8 +12047,32 @@
       <c r="J8" s="4">
         <v>1.502</v>
       </c>
+      <c r="AN8" s="1">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AO8" s="6">
+        <f t="shared" si="4"/>
+        <v>21.306224193237586</v>
+      </c>
+      <c r="AP8" s="6">
+        <f t="shared" si="5"/>
+        <v>8.8356890216850399</v>
+      </c>
+      <c r="AQ8" s="6">
+        <f t="shared" si="6"/>
+        <v>39.847648280068533</v>
+      </c>
+      <c r="AR8" s="6">
+        <f t="shared" si="2"/>
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="AS8" s="6">
+        <f t="shared" si="7"/>
+        <v>0.72355430183356839</v>
+      </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -8236,17 +12083,17 @@
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>73.574494175352541</v>
       </c>
       <c r="E9" s="4">
         <v>6.3447902158703471</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>2.5382950090458741E-4</v>
       </c>
       <c r="H9" s="1">
@@ -8258,8 +12105,32 @@
       <c r="J9" s="4">
         <v>1.46</v>
       </c>
+      <c r="AN9" s="1">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="AO9" s="6">
+        <f t="shared" si="4"/>
+        <v>69.484536808026789</v>
+      </c>
+      <c r="AP9" s="6">
+        <f t="shared" si="5"/>
+        <v>35.08352055592956</v>
+      </c>
+      <c r="AQ9" s="6">
+        <f t="shared" si="6"/>
+        <v>46.391649303823002</v>
+      </c>
+      <c r="AR9" s="6">
+        <f t="shared" si="2"/>
+        <v>0.78260869565217384</v>
+      </c>
+      <c r="AS9" s="6">
+        <f t="shared" si="7"/>
+        <v>0.7061589092618713</v>
+      </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -8270,17 +12141,17 @@
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>20.816385127051692</v>
       </c>
       <c r="E10" s="4">
         <v>1.9795058998944075</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>3.8420401139033575E-4</v>
       </c>
       <c r="H10" s="1">
@@ -8292,8 +12163,32 @@
       <c r="J10" s="4">
         <v>1.4370000000000001</v>
       </c>
+      <c r="AN10" s="1">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+      <c r="AO10" s="6">
+        <f t="shared" si="4"/>
+        <v>21.293071735131701</v>
+      </c>
+      <c r="AP10" s="6">
+        <f t="shared" si="5"/>
+        <v>5.7580131093954394</v>
+      </c>
+      <c r="AQ10" s="6">
+        <f t="shared" si="6"/>
+        <v>4.9214042425974984</v>
+      </c>
+      <c r="AR10" s="6">
+        <f t="shared" si="2"/>
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="AS10" s="6">
+        <f t="shared" si="7"/>
+        <v>0.68641278796426897</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -8304,17 +12199,17 @@
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>17.667101333445487</v>
       </c>
       <c r="E11" s="4">
         <v>3.219264329662352</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>4.6887855651876298E-5</v>
       </c>
       <c r="H11" s="1">
@@ -8326,8 +12221,32 @@
       <c r="J11" s="4">
         <v>1.6559999999999999</v>
       </c>
+      <c r="AN11" s="1">
+        <f t="shared" si="8"/>
+        <v>21</v>
+      </c>
+      <c r="AO11" s="6">
+        <f t="shared" si="4"/>
+        <v>6.0244353256447845</v>
+      </c>
+      <c r="AP11" s="6">
+        <f t="shared" si="5"/>
+        <v>1.7964377913090843</v>
+      </c>
+      <c r="AQ11" s="6">
+        <f t="shared" si="6"/>
+        <v>7.4491863433562129</v>
+      </c>
+      <c r="AR11" s="6">
+        <f t="shared" si="2"/>
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="AS11" s="6">
+        <f t="shared" si="7"/>
+        <v>0.67559943582510584</v>
+      </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -8338,17 +12257,17 @@
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>15.963635379745167</v>
       </c>
       <c r="E12" s="4">
         <v>3.005177966008191</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>1.2779120936401461E-4</v>
       </c>
       <c r="H12" s="1">
@@ -8360,8 +12279,32 @@
       <c r="J12" s="4">
         <v>1.7370000000000001</v>
       </c>
+      <c r="AN12" s="1">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="AO12" s="6">
+        <f t="shared" si="4"/>
+        <v>5.1130063517435405</v>
+      </c>
+      <c r="AP12" s="6">
+        <f t="shared" si="5"/>
+        <v>2.9215412302268198</v>
+      </c>
+      <c r="AQ12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="AR12" s="6">
+        <f t="shared" si="2"/>
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="AS12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.77856135401974613</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -8372,17 +12315,17 @@
       <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>7.0668603509873824</v>
       </c>
       <c r="E13" s="4">
         <v>1.5626443518739146</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>4.4474966741118462E-6</v>
       </c>
       <c r="H13" s="1">
@@ -8394,8 +12337,32 @@
       <c r="J13" s="4">
         <v>1.4590000000000001</v>
       </c>
+      <c r="AN13" s="1">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="AO13" s="6">
+        <f t="shared" si="4"/>
+        <v>4.6200091091930569</v>
+      </c>
+      <c r="AP13" s="6">
+        <f t="shared" si="5"/>
+        <v>2.7272539415186681</v>
+      </c>
+      <c r="AQ13" s="6">
+        <f t="shared" si="6"/>
+        <v>2.4776954518266576</v>
+      </c>
+      <c r="AR13" s="6">
+        <f t="shared" si="2"/>
+        <v>0.91304347826086962</v>
+      </c>
+      <c r="AS13" s="6">
+        <f t="shared" si="7"/>
+        <v>0.81664315937940779</v>
+      </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -8406,17 +12373,17 @@
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>12.436951564983044</v>
       </c>
       <c r="E14" s="4">
         <v>2.8765823670330759</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <v>4.6887855651876298E-5</v>
       </c>
       <c r="H14" s="1">
@@ -8428,8 +12395,31 @@
       <c r="J14" s="4">
         <v>1.6379999999999999</v>
       </c>
+      <c r="AN14" s="1">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="AO14" s="6">
+        <f t="shared" si="4"/>
+        <v>2.0452082760786618</v>
+      </c>
+      <c r="AP14" s="6">
+        <f t="shared" si="5"/>
+        <v>1.4181283158750546</v>
+      </c>
+      <c r="AQ14" s="6">
+        <v>1</v>
+      </c>
+      <c r="AR14" s="6">
+        <f t="shared" si="2"/>
+        <v>0.9565217391304347</v>
+      </c>
+      <c r="AS14" s="6">
+        <f t="shared" si="7"/>
+        <v>0.68594264221908807</v>
+      </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -8440,17 +12430,17 @@
       <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>8.095527221210272</v>
       </c>
       <c r="E15" s="4">
         <v>2.2126150321267621</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="7">
         <v>1.4986210786444661E-4</v>
       </c>
       <c r="H15" s="1">
@@ -8462,8 +12452,32 @@
       <c r="J15" s="4">
         <v>1.7050000000000001</v>
       </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="8"/>
+        <v>33</v>
+      </c>
+      <c r="AO15" s="6">
+        <f t="shared" si="4"/>
+        <v>3.5993574241691144</v>
+      </c>
+      <c r="AP15" s="6">
+        <f t="shared" si="5"/>
+        <v>2.6105510846051083</v>
+      </c>
+      <c r="AQ15" s="6">
+        <f t="shared" si="6"/>
+        <v>0.90909090909090917</v>
+      </c>
+      <c r="AR15" s="6">
+        <f t="shared" si="2"/>
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="AS15" s="6">
+        <f t="shared" si="7"/>
+        <v>0.77009873060648804</v>
+      </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -8474,17 +12488,17 @@
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>10.855405992184116</v>
       </c>
       <c r="E16" s="4">
         <v>2.5675322748057079</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>5.1576641217063925E-5</v>
       </c>
       <c r="H16" s="1">
@@ -8496,8 +12510,32 @@
       <c r="J16" s="4">
         <v>1.7070000000000001</v>
       </c>
+      <c r="AN16" s="1">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+      <c r="AO16" s="6">
+        <f t="shared" si="4"/>
+        <v>2.3429130405450831</v>
+      </c>
+      <c r="AP16" s="6">
+        <f t="shared" si="5"/>
+        <v>2.0079885902553296</v>
+      </c>
+      <c r="AQ16" s="6">
+        <f t="shared" si="6"/>
+        <v>2.9056197598005924</v>
+      </c>
+      <c r="AR16" s="6">
+        <f t="shared" si="2"/>
+        <v>0.86956521739130443</v>
+      </c>
+      <c r="AS16" s="6">
+        <f t="shared" si="7"/>
+        <v>0.80159849553361551</v>
+      </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -8508,17 +12546,17 @@
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>6.0885448377837434</v>
       </c>
       <c r="E17" s="4">
         <v>2.2312408401110857</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>4.8981773007164672E-4</v>
       </c>
       <c r="H17" s="1">
@@ -8530,8 +12568,32 @@
       <c r="J17" s="4">
         <v>1.681</v>
       </c>
+      <c r="AN17" s="1">
+        <f t="shared" si="8"/>
+        <v>39</v>
+      </c>
+      <c r="AO17" s="6">
+        <f t="shared" si="4"/>
+        <v>3.1416449558546669</v>
+      </c>
+      <c r="AP17" s="6">
+        <f t="shared" si="5"/>
+        <v>2.3300824761940815</v>
+      </c>
+      <c r="AQ17" s="6">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AR17" s="6">
+        <f t="shared" si="2"/>
+        <v>0.86956521739130443</v>
+      </c>
+      <c r="AS17" s="6">
+        <f t="shared" si="7"/>
+        <v>0.80253878702397752</v>
+      </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -8542,17 +12604,17 @@
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>11.464181780769531</v>
       </c>
       <c r="E18" s="4">
         <v>2.7825557685143458</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>4.9120610682918029E-5</v>
       </c>
       <c r="H18" s="1">
@@ -8564,8 +12626,32 @@
       <c r="J18" s="4">
         <v>1.262</v>
       </c>
+      <c r="AN18" s="1">
+        <f t="shared" si="8"/>
+        <v>42</v>
+      </c>
+      <c r="AO18" s="6">
+        <f t="shared" si="4"/>
+        <v>1.7620756139282536</v>
+      </c>
+      <c r="AP18" s="6">
+        <f t="shared" si="5"/>
+        <v>2.0248918514976886</v>
+      </c>
+      <c r="AQ18" s="6">
+        <f t="shared" si="6"/>
+        <v>9.4968908116799291</v>
+      </c>
+      <c r="AR18" s="6">
+        <f t="shared" si="2"/>
+        <v>0.9565217391304347</v>
+      </c>
+      <c r="AS18" s="6">
+        <f t="shared" si="7"/>
+        <v>0.79031499764927138</v>
+      </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="D19" s="5">
         <f>AVERAGE(D12:D18)</f>
         <v>10.281586732523323</v>
@@ -8574,17 +12660,122 @@
         <f>AVERAGE(E13:E18)</f>
         <v>2.3721951057441486</v>
       </c>
+      <c r="AN19" s="1">
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="AO19" s="6">
+        <f t="shared" si="4"/>
+        <v>3.3178297422028566</v>
+      </c>
+      <c r="AP19" s="6">
+        <f t="shared" si="5"/>
+        <v>2.5252202275582545</v>
+      </c>
+      <c r="AQ19" s="6">
+        <f t="shared" si="6"/>
+        <v>0.95238095238095244</v>
+      </c>
+      <c r="AR19" s="6">
+        <f t="shared" si="2"/>
+        <v>0.91304347826086962</v>
+      </c>
+      <c r="AS19" s="6">
+        <f t="shared" si="7"/>
+        <v>0.59332393041842979</v>
+      </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="C21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="10">
+        <f>MAX(D3:D18)</f>
+        <v>240.0916933100078</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" ref="E21:J21" si="9">MAX(E3:E18)</f>
+        <v>38.658748032082826</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="9"/>
+        <v>45</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="9"/>
+        <v>2.3927254516111322E-3</v>
+      </c>
+      <c r="H21" s="10">
+        <f t="shared" si="9"/>
+        <v>2.4E-2</v>
+      </c>
+      <c r="I21" s="10">
+        <f t="shared" si="9"/>
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="J21" s="10">
+        <f t="shared" si="9"/>
+        <v>2.1269999999999998</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="C22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="10">
+        <f>D21/D3</f>
+        <v>69.484536808026789</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" ref="E22:J22" si="10">E21/E3</f>
+        <v>35.08352055592956</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10">
+        <f t="shared" si="10"/>
+        <v>46.391649303823002</v>
+      </c>
+      <c r="H22" s="10">
+        <f t="shared" si="10"/>
+        <v>1.0434782608695652</v>
+      </c>
+      <c r="I22" s="10">
+        <f t="shared" si="10"/>
+        <v>3.9333333333333331</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B25:D25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
